--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/confirmed/2026 발주 확정.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/confirmed/2026 발주 확정.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C196"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,11 +436,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>386</v>
+        <v>119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>271</v>
+        <v>321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -466,11 +466,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>925</v>
+        <v>981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -481,11 +481,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -496,11 +496,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128</v>
+        <v>399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -511,11 +511,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>768</v>
+        <v>460</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -526,11 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>889</v>
+        <v>618</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -556,11 +556,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -571,11 +571,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>493</v>
+        <v>627</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>402</v>
+        <v>215</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -601,11 +601,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>193</v>
+        <v>331</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -616,11 +616,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>576</v>
+        <v>997</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -631,11 +631,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>768</v>
+        <v>336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -646,11 +646,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>439</v>
+        <v>762</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -661,11 +661,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>339</v>
+        <v>658</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -676,11 +676,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>436</v>
+        <v>1000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>337</v>
+        <v>810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>855</v>
+        <v>343</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -721,11 +721,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>595</v>
+        <v>297</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -736,11 +736,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>132</v>
+        <v>383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>699</v>
+        <v>964</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>833</v>
+        <v>568</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -796,11 +796,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57</v>
+        <v>708</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -811,11 +811,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>896</v>
+        <v>482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -841,11 +841,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>802</v>
+        <v>224</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -856,11 +856,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>345</v>
+        <v>826</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>576</v>
+        <v>861</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -901,11 +901,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>215</v>
+        <v>699</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -916,11 +916,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>587</v>
+        <v>152</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -931,11 +931,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>767</v>
+        <v>320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -946,11 +946,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -961,11 +961,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>387</v>
+        <v>167</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -976,11 +976,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>515</v>
+        <v>443</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -991,11 +991,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>760</v>
+        <v>85</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1006,11 +1006,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>788</v>
+        <v>622</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1021,11 +1021,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>164</v>
+        <v>606</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1036,11 +1036,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>964</v>
+        <v>557</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>34</v>
+        <v>955</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>564</v>
+        <v>438</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1081,11 +1081,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>661</v>
+        <v>47</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1096,11 +1096,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>908</v>
+        <v>728</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1111,11 +1111,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>983</v>
+        <v>618</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1126,11 +1126,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>11</v>
+        <v>946</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1141,11 +1141,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>395</v>
+        <v>121</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1156,11 +1156,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>754</v>
+        <v>683</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1171,11 +1171,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>116</v>
+        <v>373</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1186,11 +1186,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>552</v>
+        <v>672</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1201,11 +1201,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>439</v>
+        <v>55</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1216,11 +1216,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>994</v>
+        <v>670</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1231,11 +1231,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>155</v>
+        <v>672</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>296</v>
+        <v>1000</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1261,11 +1261,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>54</v>
+        <v>998</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>928</v>
+        <v>118</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>432</v>
+        <v>110</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1306,11 +1306,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>927</v>
+        <v>237</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1321,11 +1321,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>479</v>
+        <v>774</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1336,11 +1336,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>96</v>
+        <v>581</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>107</v>
+        <v>714</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1366,11 +1366,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>849</v>
+        <v>393</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>86</v>
+        <v>484</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1411,11 +1411,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1426,11 +1426,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>455</v>
+        <v>522</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>997</v>
+        <v>363</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1456,11 +1456,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>252</v>
+        <v>504</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1471,11 +1471,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>727</v>
+        <v>128</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>344</v>
+        <v>155</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>473</v>
+        <v>329</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1546,11 +1546,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>249</v>
+        <v>476</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1561,11 +1561,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>976</v>
+        <v>543</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1576,11 +1576,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>149</v>
+        <v>366</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1606,11 +1606,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>118</v>
+        <v>749</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1621,11 +1621,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1651,11 +1651,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1666,11 +1666,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>376</v>
+        <v>127</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1681,11 +1681,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>472</v>
+        <v>879</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1696,11 +1696,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>484</v>
+        <v>673</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>882</v>
+        <v>703</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1726,11 +1726,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>102</v>
+        <v>962</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1741,11 +1741,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>836</v>
+        <v>259</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1756,11 +1756,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>321</v>
+        <v>188</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1771,11 +1771,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>723</v>
+        <v>173</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>51</v>
+        <v>583</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1801,11 +1801,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>865</v>
+        <v>991</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1831,11 +1831,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>738</v>
+        <v>654</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1846,11 +1846,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>374</v>
+        <v>200</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1861,11 +1861,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>535</v>
+        <v>683</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1876,11 +1876,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>703</v>
+        <v>415</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1891,11 +1891,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>276</v>
+        <v>765</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1906,11 +1906,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>41</v>
+        <v>914</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1921,1440 +1921,15 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>885</v>
+        <v>470</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
           <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>579</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>573</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>106</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>114</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>134</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>73</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>143</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>853</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>391</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>655</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>96</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>610</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>949</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>32</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>212</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>464</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>104</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>135</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>974</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>61</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>956</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>453</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>414</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>40</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>709</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>186</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>229</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>291</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>466</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>45</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>644</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>261</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>312</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>431</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>500</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>99</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>402</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>439</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>668</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>265</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>831</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>823</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>401</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>377</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>567</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>362</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>524</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>407</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>194</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>336</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>234</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>927</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>69</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>552</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>795</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>248</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>112</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>682</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>282</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>845</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>67</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>599</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>373</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>190</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>616</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>835</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>724</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>945</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>38</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>727</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>980</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>587</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>586</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>866</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>565</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>189</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>48</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>67</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>626</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>30</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>499</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>349</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>216</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>358</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>191</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>70</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>161</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>731</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>802</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>876</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>891</v>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>993</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>392</v>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>974</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>415</v>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
         </is>
       </c>
     </row>
